--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260907.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260907.xlsx
@@ -887,17 +887,17 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>5,285,520</t>
+          <t>1,996,288</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -909,17 +909,17 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>1,996,288</t>
+          <t>5,285,520</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -1019,17 +1019,17 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>1,335,000</t>
+          <t>601,600</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -1041,17 +1041,17 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>601,600</t>
+          <t>1,335,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1085,17 +1085,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>3481</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>群創</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>12,847,134</t>
+          <t>312,672</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1107,17 +1107,17 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>3481</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>群創</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>312,672</t>
+          <t>12,847,134</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1173,17 +1173,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>999,822</t>
+          <t>1,998,587</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1217,17 +1217,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>1,998,587</t>
+          <t>999,822</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>和碩</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>1,194,441</t>
+          <t>3,472,981</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>和碩</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>3,472,981</t>
+          <t>1,194,441</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>仁寶</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>7,152,249</t>
+          <t>2,591,703</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>2324</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>仁寶</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>2,591,703</t>
+          <t>7,152,249</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1591,17 +1591,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>581,000</t>
+          <t>145,386</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>145,386</t>
+          <t>581,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1657,17 +1657,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>6213</t>
+          <t>202609WVHFU6F</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>富邦科技ETF期貨</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>389,000</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1679,17 +1679,17 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>202609WVHFU6F</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>富邦科技ETF期貨</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>2,185,107</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1701,17 +1701,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>2,185,107</t>
+          <t>389,000</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1789,17 +1789,17 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>774,000</t>
+          <t>319,000</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -1811,17 +1811,17 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>290,000</t>
+          <t>802,000</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -1833,17 +1833,17 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>宏碁</t>
+          <t>華新科</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>4,948,956</t>
+          <t>496,000</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -1855,17 +1855,17 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>319,000</t>
+          <t>290,000</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -1877,17 +1877,17 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>宏碁</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>802,000</t>
+          <t>4,948,956</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -1899,17 +1899,17 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>華新科</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>496,000</t>
+          <t>774,000</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -1943,17 +1943,17 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>鴻準</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>1,001,121</t>
+          <t>1,754,000</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -1965,17 +1965,17 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>鴻準</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>1,754,000</t>
+          <t>1,001,121</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -2009,17 +2009,17 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>156,000</t>
+          <t>65,538</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -2031,17 +2031,17 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>330,000</t>
+          <t>156,000</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -2053,17 +2053,17 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>65,538</t>
+          <t>330,000</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -2075,17 +2075,17 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>神基</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>170,000</t>
+          <t>678,000</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -2119,17 +2119,17 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>神基</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>678,000</t>
+          <t>170,000</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
